--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2022/Airline_Cumulative_Statistics_2022.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2022/Airline_Cumulative_Statistics_2022.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="37" uniqueCount="37">
   <si>
     <t>Row</t>
   </si>
@@ -25,6 +25,9 @@
   </si>
   <si>
     <t>American</t>
+  </si>
+  <si>
+    <t>Avelo</t>
   </si>
   <si>
     <t>Breeze</t>
@@ -166,7 +169,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
@@ -189,40 +192,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
@@ -353,19 +356,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>647666426</v>
+        <v>995035291</v>
       </c>
       <c r="C5" s="0">
-        <v>918104620</v>
+        <v>1341707633</v>
       </c>
       <c r="D5" s="0">
         <v>0</v>
       </c>
       <c r="E5" s="0">
-        <v>119</v>
+        <v>165</v>
       </c>
       <c r="F5" s="0">
-        <v>9416</v>
+        <v>10480</v>
       </c>
       <c r="G5" s="0">
         <v>0</v>
@@ -374,10 +377,10 @@
         <v>0</v>
       </c>
       <c r="I5" s="0">
-        <v>70.540000000000006</v>
+        <v>74.159999999999997</v>
       </c>
       <c r="J5" s="0">
-        <v>806</v>
+        <v>787</v>
       </c>
       <c r="K5" s="0">
         <v>0</v>
@@ -394,40 +397,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>181848269733</v>
+        <v>647863356</v>
       </c>
       <c r="C6" s="0">
-        <v>216006867346</v>
+        <v>918464350</v>
       </c>
       <c r="D6" s="0">
-        <v>694154</v>
+        <v>0</v>
       </c>
       <c r="E6" s="0">
-        <v>168</v>
+        <v>119</v>
       </c>
       <c r="F6" s="0">
-        <v>999532</v>
+        <v>9418</v>
       </c>
       <c r="G6" s="0">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="H6" s="0">
-        <v>9.2300000000000004</v>
+        <v>0</v>
       </c>
       <c r="I6" s="0">
-        <v>84.189999999999998</v>
+        <v>70.540000000000006</v>
       </c>
       <c r="J6" s="0">
-        <v>1136</v>
+        <v>806</v>
       </c>
       <c r="K6" s="0">
-        <v>6840.1099999999997</v>
+        <v>0</v>
       </c>
       <c r="L6" s="0">
-        <v>37.030000000000001</v>
+        <v>0</v>
       </c>
       <c r="M6" s="0">
-        <v>0.090999999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -435,40 +438,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>25643877882</v>
+        <v>181848269733</v>
       </c>
       <c r="C7" s="0">
-        <v>31714377680</v>
+        <v>216006867346</v>
       </c>
       <c r="D7" s="0">
-        <v>777694</v>
+        <v>694154</v>
       </c>
       <c r="E7" s="0">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="F7" s="0">
-        <v>165438</v>
+        <v>999532</v>
       </c>
       <c r="G7" s="0">
-        <v>4.0599999999999996</v>
+        <v>3.21</v>
       </c>
       <c r="H7" s="0">
-        <v>11.06</v>
+        <v>9.2300000000000004</v>
       </c>
       <c r="I7" s="0">
-        <v>80.859999999999999</v>
+        <v>84.189999999999998</v>
       </c>
       <c r="J7" s="0">
-        <v>990</v>
+        <v>1136</v>
       </c>
       <c r="K7" s="0">
-        <v>5412.7299999999996</v>
+        <v>6840.1099999999997</v>
       </c>
       <c r="L7" s="0">
-        <v>27.949999999999999</v>
+        <v>37.030000000000001</v>
       </c>
       <c r="M7" s="0">
-        <v>0.076999999999999999</v>
+        <v>0.090999999999999998</v>
       </c>
     </row>
     <row r="8">
@@ -476,40 +479,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>14938665984</v>
+        <v>25643877882</v>
       </c>
       <c r="C8" s="0">
-        <v>18646481586</v>
+        <v>31714377680</v>
       </c>
       <c r="D8" s="0">
-        <v>836540</v>
+        <v>777694</v>
       </c>
       <c r="E8" s="0">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="F8" s="0">
-        <v>75622</v>
+        <v>165438</v>
       </c>
       <c r="G8" s="0">
-        <v>3.3900000000000001</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="H8" s="0">
-        <v>8.7300000000000004</v>
+        <v>11.06</v>
       </c>
       <c r="I8" s="0">
-        <v>80.120000000000005</v>
+        <v>80.859999999999999</v>
       </c>
       <c r="J8" s="0">
-        <v>1053</v>
+        <v>990</v>
       </c>
       <c r="K8" s="0">
-        <v>8522.6700000000001</v>
+        <v>5412.7299999999996</v>
       </c>
       <c r="L8" s="0">
-        <v>38.43</v>
+        <v>27.949999999999999</v>
       </c>
       <c r="M8" s="0">
-        <v>0.088999999999999996</v>
+        <v>0.076999999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -517,40 +520,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>52577079315</v>
+        <v>14938665984</v>
       </c>
       <c r="C9" s="0">
-        <v>64502706105</v>
+        <v>18646481586</v>
       </c>
       <c r="D9" s="0">
-        <v>620278</v>
+        <v>836540</v>
       </c>
       <c r="E9" s="0">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="F9" s="0">
-        <v>333701</v>
+        <v>75622</v>
       </c>
       <c r="G9" s="0">
-        <v>3.21</v>
+        <v>3.3900000000000001</v>
       </c>
       <c r="H9" s="0">
-        <v>10.130000000000001</v>
+        <v>8.7300000000000004</v>
       </c>
       <c r="I9" s="0">
-        <v>81.510000000000005</v>
+        <v>80.120000000000005</v>
       </c>
       <c r="J9" s="0">
-        <v>1210</v>
+        <v>1053</v>
       </c>
       <c r="K9" s="0">
-        <v>5683.2600000000002</v>
+        <v>8522.6700000000001</v>
       </c>
       <c r="L9" s="0">
-        <v>36.109999999999999</v>
+        <v>38.43</v>
       </c>
       <c r="M9" s="0">
-        <v>0.092999999999999999</v>
+        <v>0.088999999999999996</v>
       </c>
     </row>
     <row r="10">
@@ -558,40 +561,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>123865585444</v>
+        <v>52577079315</v>
       </c>
       <c r="C10" s="0">
-        <v>148494970073</v>
+        <v>64502706105</v>
       </c>
       <c r="D10" s="0">
-        <v>555121</v>
+        <v>620278</v>
       </c>
       <c r="E10" s="0">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="F10" s="0">
-        <v>1298423</v>
+        <v>333701</v>
       </c>
       <c r="G10" s="0">
-        <v>4.8499999999999996</v>
+        <v>3.21</v>
       </c>
       <c r="H10" s="0">
-        <v>9.6600000000000001</v>
+        <v>10.130000000000001</v>
       </c>
       <c r="I10" s="0">
-        <v>83.409999999999997</v>
+        <v>81.510000000000005</v>
       </c>
       <c r="J10" s="0">
-        <v>728</v>
+        <v>1210</v>
       </c>
       <c r="K10" s="0">
-        <v>4827.8900000000003</v>
+        <v>5683.2600000000002</v>
       </c>
       <c r="L10" s="0">
-        <v>30.809999999999999</v>
+        <v>36.109999999999999</v>
       </c>
       <c r="M10" s="0">
-        <v>0.084000000000000005</v>
+        <v>0.092999999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -599,40 +602,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>39778287959</v>
+        <v>123865585444</v>
       </c>
       <c r="C11" s="0">
-        <v>48572965624</v>
+        <v>148494970073</v>
       </c>
       <c r="D11" s="0">
-        <v>736400</v>
+        <v>555121</v>
       </c>
       <c r="E11" s="0">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="F11" s="0">
-        <v>259625</v>
+        <v>1298423</v>
       </c>
       <c r="G11" s="0">
-        <v>3.9399999999999999</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="H11" s="0">
-        <v>10.640000000000001</v>
+        <v>9.6600000000000001</v>
       </c>
       <c r="I11" s="0">
-        <v>81.890000000000001</v>
+        <v>83.409999999999997</v>
       </c>
       <c r="J11" s="0">
-        <v>1019</v>
+        <v>728</v>
       </c>
       <c r="K11" s="0">
-        <v>4989.3599999999997</v>
+        <v>4827.8900000000003</v>
       </c>
       <c r="L11" s="0">
-        <v>27.140000000000001</v>
+        <v>30.809999999999999</v>
       </c>
       <c r="M11" s="0">
-        <v>0.071999999999999995</v>
+        <v>0.084000000000000005</v>
       </c>
     </row>
     <row r="12">
@@ -640,40 +643,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>5215777397</v>
+        <v>39778287959</v>
       </c>
       <c r="C12" s="0">
-        <v>6705092128</v>
+        <v>48572965624</v>
       </c>
       <c r="D12" s="0">
-        <v>383148</v>
+        <v>736400</v>
       </c>
       <c r="E12" s="0">
         <v>184</v>
       </c>
       <c r="F12" s="0">
-        <v>31389</v>
+        <v>259625</v>
       </c>
       <c r="G12" s="0">
-        <v>1.79</v>
+        <v>3.9399999999999999</v>
       </c>
       <c r="H12" s="0">
-        <v>5.3499999999999996</v>
+        <v>10.640000000000001</v>
       </c>
       <c r="I12" s="0">
-        <v>77.790000000000006</v>
+        <v>81.890000000000001</v>
       </c>
       <c r="J12" s="0">
-        <v>1165</v>
+        <v>1019</v>
       </c>
       <c r="K12" s="0">
-        <v>5994.9899999999998</v>
+        <v>4989.3599999999997</v>
       </c>
       <c r="L12" s="0">
-        <v>32.670000000000002</v>
+        <v>27.140000000000001</v>
       </c>
       <c r="M12" s="0">
-        <v>0.084000000000000005</v>
+        <v>0.071999999999999995</v>
       </c>
     </row>
     <row r="13">
@@ -681,40 +684,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>190203737941</v>
+        <v>5215777397</v>
       </c>
       <c r="C13" s="0">
-        <v>228090827297</v>
+        <v>6705092128</v>
       </c>
       <c r="D13" s="0">
-        <v>751733</v>
+        <v>383148</v>
       </c>
       <c r="E13" s="0">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="F13" s="0">
-        <v>775850</v>
+        <v>31389</v>
       </c>
       <c r="G13" s="0">
-        <v>2.5600000000000001</v>
+        <v>1.79</v>
       </c>
       <c r="H13" s="0">
-        <v>9.2100000000000009</v>
+        <v>5.3499999999999996</v>
       </c>
       <c r="I13" s="0">
-        <v>83.390000000000001</v>
+        <v>77.790000000000006</v>
       </c>
       <c r="J13" s="0">
-        <v>1495</v>
+        <v>1165</v>
       </c>
       <c r="K13" s="0">
-        <v>7561.9200000000001</v>
+        <v>5994.9899999999998</v>
       </c>
       <c r="L13" s="0">
-        <v>39.630000000000003</v>
+        <v>32.670000000000002</v>
       </c>
       <c r="M13" s="0">
-        <v>0.092999999999999999</v>
+        <v>0.084000000000000005</v>
       </c>
     </row>
     <row r="14">
@@ -722,40 +725,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>1327042228</v>
+        <v>190203737941</v>
       </c>
       <c r="C14" s="0">
-        <v>1588069800</v>
+        <v>228090827297</v>
       </c>
       <c r="D14" s="0">
-        <v>64477</v>
+        <v>751733</v>
       </c>
       <c r="E14" s="0">
-        <v>50</v>
+        <v>174</v>
       </c>
       <c r="F14" s="0">
-        <v>77673</v>
+        <v>775850</v>
       </c>
       <c r="G14" s="0">
-        <v>3.1499999999999999</v>
+        <v>2.5600000000000001</v>
       </c>
       <c r="H14" s="0">
-        <v>4.9400000000000004</v>
+        <v>9.2100000000000009</v>
       </c>
       <c r="I14" s="0">
-        <v>83.560000000000002</v>
+        <v>83.390000000000001</v>
       </c>
       <c r="J14" s="0">
-        <v>409</v>
+        <v>1495</v>
       </c>
       <c r="K14" s="0">
-        <v>1775.01</v>
+        <v>7561.9200000000001</v>
       </c>
       <c r="L14" s="0">
-        <v>35.5</v>
+        <v>39.630000000000003</v>
       </c>
       <c r="M14" s="0">
-        <v>0.13600000000000001</v>
+        <v>0.092999999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -763,40 +766,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>5348119841</v>
+        <v>1327042228</v>
       </c>
       <c r="C15" s="0">
-        <v>6940528769</v>
+        <v>1588069800</v>
       </c>
       <c r="D15" s="0">
-        <v>112689</v>
+        <v>64477</v>
       </c>
       <c r="E15" s="0">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="F15" s="0">
-        <v>235833</v>
+        <v>77673</v>
       </c>
       <c r="G15" s="0">
-        <v>3.8300000000000001</v>
+        <v>3.1499999999999999</v>
       </c>
       <c r="H15" s="0">
-        <v>6.0899999999999999</v>
+        <v>4.9400000000000004</v>
       </c>
       <c r="I15" s="0">
-        <v>77.060000000000002</v>
+        <v>83.560000000000002</v>
       </c>
       <c r="J15" s="0">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="K15" s="0">
-        <v>1854.4300000000001</v>
+        <v>1775.01</v>
       </c>
       <c r="L15" s="0">
-        <v>26.510000000000002</v>
+        <v>35.5</v>
       </c>
       <c r="M15" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.13600000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -804,40 +807,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>7687341757</v>
+        <v>5348119841</v>
       </c>
       <c r="C16" s="0">
-        <v>9393408708</v>
+        <v>6940528769</v>
       </c>
       <c r="D16" s="0">
-        <v>56261</v>
+        <v>112689</v>
       </c>
       <c r="E16" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F16" s="0">
-        <v>261319</v>
+        <v>235833</v>
       </c>
       <c r="G16" s="0">
-        <v>1.5700000000000001</v>
+        <v>3.8300000000000001</v>
       </c>
       <c r="H16" s="0">
-        <v>2.71</v>
+        <v>6.0899999999999999</v>
       </c>
       <c r="I16" s="0">
-        <v>81.840000000000003</v>
+        <v>77.060000000000002</v>
       </c>
       <c r="J16" s="0">
-        <v>510</v>
+        <v>417</v>
       </c>
       <c r="K16" s="0">
-        <v>2020.0599999999999</v>
+        <v>1854.4300000000001</v>
       </c>
       <c r="L16" s="0">
-        <v>29.34</v>
+        <v>26.510000000000002</v>
       </c>
       <c r="M16" s="0">
-        <v>0.097000000000000003</v>
+        <v>0.10000000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -845,40 +848,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>678924451</v>
+        <v>7687341757</v>
       </c>
       <c r="C17" s="0">
-        <v>894214450</v>
+        <v>9393408708</v>
       </c>
       <c r="D17" s="0">
-        <v>39778</v>
+        <v>56261</v>
       </c>
       <c r="E17" s="0">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="F17" s="0">
-        <v>52916</v>
+        <v>261319</v>
       </c>
       <c r="G17" s="0">
-        <v>2.3500000000000001</v>
+        <v>1.5700000000000001</v>
       </c>
       <c r="H17" s="0">
-        <v>3.6499999999999999</v>
+        <v>2.71</v>
       </c>
       <c r="I17" s="0">
-        <v>75.920000000000002</v>
+        <v>81.840000000000003</v>
       </c>
       <c r="J17" s="0">
-        <v>338</v>
+        <v>510</v>
       </c>
       <c r="K17" s="0">
-        <v>2549.9200000000001</v>
+        <v>2020.0599999999999</v>
       </c>
       <c r="L17" s="0">
-        <v>51</v>
+        <v>29.34</v>
       </c>
       <c r="M17" s="0">
-        <v>0.23400000000000001</v>
+        <v>0.097000000000000003</v>
       </c>
     </row>
     <row r="18">
@@ -886,40 +889,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>1576481803</v>
+        <v>678924451</v>
       </c>
       <c r="C18" s="0">
-        <v>1925305568</v>
+        <v>894214450</v>
       </c>
       <c r="D18" s="0">
-        <v>209272</v>
+        <v>39778</v>
       </c>
       <c r="E18" s="0">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="F18" s="0">
-        <v>46256</v>
+        <v>52916</v>
       </c>
       <c r="G18" s="0">
-        <v>5.0300000000000002</v>
+        <v>2.3500000000000001</v>
       </c>
       <c r="H18" s="0">
-        <v>8.7400000000000002</v>
+        <v>3.6499999999999999</v>
       </c>
       <c r="I18" s="0">
-        <v>81.879999999999995</v>
+        <v>75.920000000000002</v>
       </c>
       <c r="J18" s="0">
-        <v>548</v>
+        <v>338</v>
       </c>
       <c r="K18" s="0">
-        <v>1545.9000000000001</v>
+        <v>2549.9200000000001</v>
       </c>
       <c r="L18" s="0">
-        <v>20.34</v>
+        <v>51</v>
       </c>
       <c r="M18" s="0">
-        <v>0.065000000000000002</v>
+        <v>0.23400000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -927,40 +930,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>4967942041</v>
+        <v>2309904293</v>
       </c>
       <c r="C19" s="0">
-        <v>5783728526</v>
+        <v>2873143368</v>
       </c>
       <c r="D19" s="0">
-        <v>197061</v>
+        <v>168118</v>
       </c>
       <c r="E19" s="0">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F19" s="0">
-        <v>120233</v>
+        <v>94451</v>
       </c>
       <c r="G19" s="0">
-        <v>4.0999999999999996</v>
+        <v>5.5300000000000002</v>
       </c>
       <c r="H19" s="0">
-        <v>7.9400000000000004</v>
+        <v>8.0899999999999999</v>
       </c>
       <c r="I19" s="0">
-        <v>85.900000000000006</v>
+        <v>80.400000000000006</v>
       </c>
       <c r="J19" s="0">
-        <v>628</v>
+        <v>400</v>
       </c>
       <c r="K19" s="0">
-        <v>1588.3499999999999</v>
+        <v>1846.2</v>
       </c>
       <c r="L19" s="0">
-        <v>20.739999999999998</v>
+        <v>24.289999999999999</v>
       </c>
       <c r="M19" s="0">
-        <v>0.064000000000000001</v>
+        <v>0.088999999999999996</v>
       </c>
     </row>
     <row r="20">
@@ -968,40 +971,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>1054575762</v>
+        <v>4967942041</v>
       </c>
       <c r="C20" s="0">
-        <v>1285366524</v>
+        <v>5783728526</v>
       </c>
       <c r="D20" s="0">
-        <v>71768</v>
+        <v>197061</v>
       </c>
       <c r="E20" s="0">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="F20" s="0">
-        <v>89093</v>
+        <v>120233</v>
       </c>
       <c r="G20" s="0">
-        <v>4.9699999999999998</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="H20" s="0">
-        <v>7.0199999999999996</v>
+        <v>7.9400000000000004</v>
       </c>
       <c r="I20" s="0">
-        <v>82.040000000000006</v>
+        <v>85.900000000000006</v>
       </c>
       <c r="J20" s="0">
-        <v>289</v>
+        <v>628</v>
       </c>
       <c r="K20" s="0">
-        <v>2136.4499999999998</v>
+        <v>1648.77</v>
       </c>
       <c r="L20" s="0">
-        <v>42.729999999999997</v>
+        <v>21.530000000000001</v>
       </c>
       <c r="M20" s="0">
-        <v>0.20899999999999999</v>
+        <v>0.066000000000000003</v>
       </c>
     </row>
     <row r="21">
@@ -1009,40 +1012,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>5154397478</v>
+        <v>1054575762</v>
       </c>
       <c r="C21" s="0">
-        <v>6395119229</v>
+        <v>1285366524</v>
       </c>
       <c r="D21" s="0">
-        <v>156935</v>
+        <v>71768</v>
       </c>
       <c r="E21" s="0">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="F21" s="0">
-        <v>211341</v>
+        <v>89093</v>
       </c>
       <c r="G21" s="0">
-        <v>5.1900000000000004</v>
+        <v>4.9699999999999998</v>
       </c>
       <c r="H21" s="0">
-        <v>8.4000000000000004</v>
+        <v>7.0199999999999996</v>
       </c>
       <c r="I21" s="0">
-        <v>80.599999999999994</v>
+        <v>82.040000000000006</v>
       </c>
       <c r="J21" s="0">
-        <v>421</v>
+        <v>289</v>
       </c>
       <c r="K21" s="0">
-        <v>2247.7399999999998</v>
+        <v>2136.4499999999998</v>
       </c>
       <c r="L21" s="0">
-        <v>31.309999999999999</v>
+        <v>42.729999999999997</v>
       </c>
       <c r="M21" s="0">
-        <v>0.12</v>
+        <v>0.20899999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1050,40 +1053,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>8617925827</v>
+        <v>5154397478</v>
       </c>
       <c r="C22" s="0">
-        <v>12109837910</v>
+        <v>6395119229</v>
       </c>
       <c r="D22" s="0">
-        <v>144872</v>
+        <v>156935</v>
       </c>
       <c r="E22" s="0">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F22" s="0">
-        <v>316943</v>
+        <v>211341</v>
       </c>
       <c r="G22" s="0">
-        <v>3.79</v>
+        <v>5.1900000000000004</v>
       </c>
       <c r="H22" s="0">
-        <v>7.1600000000000001</v>
+        <v>8.4000000000000004</v>
       </c>
       <c r="I22" s="0">
-        <v>71.159999999999997</v>
+        <v>80.599999999999994</v>
       </c>
       <c r="J22" s="0">
-        <v>513</v>
+        <v>421</v>
       </c>
       <c r="K22" s="0">
-        <v>1505.6099999999999</v>
+        <v>2247.7399999999998</v>
       </c>
       <c r="L22" s="0">
-        <v>20.23</v>
+        <v>31.309999999999999</v>
       </c>
       <c r="M22" s="0">
-        <v>0.073999999999999996</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="23">
@@ -1091,40 +1094,40 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>20664739993</v>
+        <v>8617925827</v>
       </c>
       <c r="C23" s="0">
-        <v>25078263825</v>
+        <v>12109837910</v>
       </c>
       <c r="D23" s="0">
-        <v>115456</v>
+        <v>144872</v>
       </c>
       <c r="E23" s="0">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F23" s="0">
-        <v>744717</v>
+        <v>316943</v>
       </c>
       <c r="G23" s="0">
-        <v>3.4300000000000002</v>
+        <v>3.79</v>
       </c>
       <c r="H23" s="0">
-        <v>5.8200000000000003</v>
+        <v>7.1600000000000001</v>
       </c>
       <c r="I23" s="0">
-        <v>82.400000000000006</v>
+        <v>71.159999999999997</v>
       </c>
       <c r="J23" s="0">
-        <v>494</v>
+        <v>513</v>
       </c>
       <c r="K23" s="0">
-        <v>1622.53</v>
+        <v>1505.6099999999999</v>
       </c>
       <c r="L23" s="0">
-        <v>24</v>
+        <v>20.23</v>
       </c>
       <c r="M23" s="0">
-        <v>0.082000000000000003</v>
+        <v>0.073999999999999996</v>
       </c>
     </row>
     <row r="24">
@@ -1132,39 +1135,80 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>945598883453</v>
+        <v>20664739993</v>
       </c>
       <c r="C24" s="0">
-        <v>1138348972274</v>
+        <v>25078263825</v>
       </c>
       <c r="D24" s="0">
-        <v>504554</v>
+        <v>115456</v>
       </c>
       <c r="E24" s="0">
-        <v>139</v>
+        <v>67</v>
       </c>
       <c r="F24" s="0">
-        <v>7508763</v>
+        <v>744717</v>
       </c>
       <c r="G24" s="0">
-        <v>3.3300000000000001</v>
+        <v>3.4300000000000002</v>
       </c>
       <c r="H24" s="0">
-        <v>8.2699999999999996</v>
+        <v>5.8200000000000003</v>
       </c>
       <c r="I24" s="0">
-        <v>83.069999999999993</v>
+        <v>82.400000000000006</v>
       </c>
       <c r="J24" s="0">
-        <v>915</v>
+        <v>494</v>
       </c>
       <c r="K24" s="0">
-        <v>5538.1599999999999</v>
+        <v>1622.53</v>
       </c>
       <c r="L24" s="0">
-        <v>35.289999999999999</v>
+        <v>24</v>
       </c>
       <c r="M24" s="0">
+        <v>0.082000000000000003</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="0">
+        <v>947327538164</v>
+      </c>
+      <c r="C25" s="0">
+        <v>1140638877437</v>
+      </c>
+      <c r="D25" s="0">
+        <v>503807</v>
+      </c>
+      <c r="E25" s="0">
+        <v>138</v>
+      </c>
+      <c r="F25" s="0">
+        <v>7567440</v>
+      </c>
+      <c r="G25" s="0">
+        <v>3.3399999999999999</v>
+      </c>
+      <c r="H25" s="0">
+        <v>8.2799999999999994</v>
+      </c>
+      <c r="I25" s="0">
+        <v>83.049999999999997</v>
+      </c>
+      <c r="J25" s="0">
+        <v>911</v>
+      </c>
+      <c r="K25" s="0">
+        <v>5521.6800000000003</v>
+      </c>
+      <c r="L25" s="0">
+        <v>35.240000000000002</v>
+      </c>
+      <c r="M25" s="0">
         <v>0.090999999999999998</v>
       </c>
     </row>

--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2022/Airline_Cumulative_Statistics_2022.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2022/Airline_Cumulative_Statistics_2022.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="41" uniqueCount="41">
   <si>
     <t>Row</t>
   </si>
@@ -85,6 +85,18 @@
   </si>
   <si>
     <t>SkyWest</t>
+  </si>
+  <si>
+    <t>FSC</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>ULCC</t>
+  </si>
+  <si>
+    <t>Regional</t>
   </si>
   <si>
     <t>All Airlines</t>
@@ -169,7 +181,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
@@ -192,40 +204,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2">
@@ -1176,39 +1188,203 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
+        <v>563551473515</v>
+      </c>
+      <c r="C25" s="0">
+        <v>673983598597</v>
+      </c>
+      <c r="D25" s="0">
+        <v>716714</v>
+      </c>
+      <c r="E25" s="0">
+        <v>171</v>
+      </c>
+      <c r="F25" s="0">
+        <v>2826353</v>
+      </c>
+      <c r="G25" s="0">
+        <v>3.0099999999999998</v>
+      </c>
+      <c r="H25" s="0">
+        <v>9.3599999999999994</v>
+      </c>
+      <c r="I25" s="0">
+        <v>83.620000000000005</v>
+      </c>
+      <c r="J25" s="0">
+        <v>1244</v>
+      </c>
+      <c r="K25" s="0">
+        <v>7310.6400000000003</v>
+      </c>
+      <c r="L25" s="0">
+        <v>39.229999999999997</v>
+      </c>
+      <c r="M25" s="0">
+        <v>0.095000000000000001</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>238844000811</v>
+      </c>
+      <c r="C26" s="0">
+        <v>287846806948</v>
+      </c>
+      <c r="D26" s="0">
+        <v>604492</v>
+      </c>
+      <c r="E26" s="0">
+        <v>156</v>
+      </c>
+      <c r="F26" s="0">
+        <v>1955443</v>
+      </c>
+      <c r="G26" s="0">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="H26" s="0">
+        <v>9.8100000000000005</v>
+      </c>
+      <c r="I26" s="0">
+        <v>82.980000000000004</v>
+      </c>
+      <c r="J26" s="0">
+        <v>901</v>
+      </c>
+      <c r="K26" s="0">
+        <v>5251.9099999999999</v>
+      </c>
+      <c r="L26" s="0">
+        <v>32.5</v>
+      </c>
+      <c r="M26" s="0">
+        <v>0.085000000000000006</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>87121150167</v>
+      </c>
+      <c r="C27" s="0">
+        <v>106466790783</v>
+      </c>
+      <c r="D27" s="0">
+        <v>641675</v>
+      </c>
+      <c r="E27" s="0">
+        <v>185</v>
+      </c>
+      <c r="F27" s="0">
+        <v>581125</v>
+      </c>
+      <c r="G27" s="0">
+        <v>3.5</v>
+      </c>
+      <c r="H27" s="0">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="I27" s="0">
+        <v>81.829999999999998</v>
+      </c>
+      <c r="J27" s="0">
+        <v>991</v>
+      </c>
+      <c r="K27" s="0">
+        <v>5171.1800000000003</v>
+      </c>
+      <c r="L27" s="0">
+        <v>27.949999999999999</v>
+      </c>
+      <c r="M27" s="0">
+        <v>0.074999999999999997</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
+        <v>57810913671</v>
+      </c>
+      <c r="C28" s="0">
+        <v>72341681109</v>
+      </c>
+      <c r="D28" s="0">
+        <v>106141</v>
+      </c>
+      <c r="E28" s="0">
+        <v>68</v>
+      </c>
+      <c r="F28" s="0">
+        <v>2204519</v>
+      </c>
+      <c r="G28" s="0">
+        <v>3.23</v>
+      </c>
+      <c r="H28" s="0">
+        <v>5.4800000000000004</v>
+      </c>
+      <c r="I28" s="0">
+        <v>79.909999999999997</v>
+      </c>
+      <c r="J28" s="0">
+        <v>472</v>
+      </c>
+      <c r="K28" s="0">
+        <v>1785.0799999999999</v>
+      </c>
+      <c r="L28" s="0">
+        <v>25.949999999999999</v>
+      </c>
+      <c r="M28" s="0">
+        <v>0.091999999999999998</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0">
         <v>947327538164</v>
       </c>
-      <c r="C25" s="0">
+      <c r="C29" s="0">
         <v>1140638877437</v>
       </c>
-      <c r="D25" s="0">
+      <c r="D29" s="0">
         <v>503807</v>
       </c>
-      <c r="E25" s="0">
+      <c r="E29" s="0">
         <v>138</v>
       </c>
-      <c r="F25" s="0">
+      <c r="F29" s="0">
         <v>7567440</v>
       </c>
-      <c r="G25" s="0">
+      <c r="G29" s="0">
         <v>3.3399999999999999</v>
       </c>
-      <c r="H25" s="0">
+      <c r="H29" s="0">
         <v>8.2799999999999994</v>
       </c>
-      <c r="I25" s="0">
+      <c r="I29" s="0">
         <v>83.049999999999997</v>
       </c>
-      <c r="J25" s="0">
+      <c r="J29" s="0">
         <v>911</v>
       </c>
-      <c r="K25" s="0">
+      <c r="K29" s="0">
         <v>5521.6800000000003</v>
       </c>
-      <c r="L25" s="0">
+      <c r="L29" s="0">
         <v>35.240000000000002</v>
       </c>
-      <c r="M25" s="0">
+      <c r="M29" s="0">
         <v>0.090999999999999998</v>
       </c>
     </row>
